--- a/outputs/ml-comparison-shared-split/ml_algorithm_results.xlsx
+++ b/outputs/ml-comparison-shared-split/ml_algorithm_results.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Metrics'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'XGB by Liquid'!$A$1:$H$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'XGB Predictions'!$A$1:$J$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'XGB Predictions'!$A$1:$J$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Split Rows'!$A$1:$C$391</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Datasets'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Configuration'!$A$1:$B$12</definedName>
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="XGBPredictionsTable" displayName="XGBPredictionsTable" ref="A1:J157" headerRowCount="1">
-  <autoFilter ref="A1:J157"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="XGBPredictionsTable" displayName="XGBPredictionsTable" ref="A1:J142" headerRowCount="1">
+  <autoFilter ref="A1:J142"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Dataset"/>
     <tableColumn id="2" name="Split"/>
@@ -571,7 +571,7 @@
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -647,35 +647,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.4121053383088759</v>
+        <v>0.4679830080978444</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.5411509080732965</v>
+        <v>0.4451622102221809</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.24239187200174</v>
+        <v>0.8853918310677119</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.377801862976621</v>
+        <v>0.7437684964953046</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.931621764388689</v>
+        <v>0.9709848797060088</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.8532446697614168</v>
+        <v>0.9572342682890155</v>
       </c>
     </row>
     <row r="3">
@@ -689,35 +689,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.4714602776900032</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.5372977600121799</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.970333632921312</v>
+        <v>1.377614079435872</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.603321178520027</v>
+        <v>1.417167851310166</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.8280190954980876</v>
+        <v>0.9297561188507677</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.4760668814719413</v>
+        <v>0.8447388022361562</v>
       </c>
     </row>
     <row r="4">
@@ -731,35 +731,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
         <v>42</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8001670285930573</v>
+        <v>0.6043829160730932</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.384349764656433</v>
+        <v>0.7075913077162266</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.933862457015711</v>
+        <v>2.040023026692671</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.91625247470343</v>
+        <v>2.616825353766693</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.8343269559314792</v>
+        <v>0.8459635528358119</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.3425381015773061</v>
+        <v>0.4706172001369925</v>
       </c>
     </row>
     <row r="5">
@@ -777,31 +777,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
         <v>42</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.016382522837747</v>
+        <v>0.9153392344643816</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.291880340150533</v>
+        <v>1.203703904230022</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.482818652847415</v>
+        <v>1.265149095109176</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.803597594114069</v>
+        <v>1.746985798446739</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.9025960052908232</v>
+        <v>0.9407570368538196</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.7485222052034487</v>
+        <v>0.7640613458158985</v>
       </c>
     </row>
     <row r="6">
@@ -819,31 +819,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
         <v>42</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.803258550386407</v>
+        <v>1.811640014959316</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.183813131662352</v>
+        <v>2.144650564526655</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3.192991347077931</v>
+        <v>3.425542020224752</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.859729768149563</v>
+        <v>2.818210410594938</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.5483560774539995</v>
+        <v>0.5656778759592624</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.3677769274720452</v>
+        <v>0.3860016861454556</v>
       </c>
     </row>
     <row r="7">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>36</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.06930430702866408</v>
+        <v>0.06423845125828263</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.07015926528444973</v>
+        <v>0.06320285787391408</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.09873650002926547</v>
+        <v>0.09311391985888448</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1320884465114109</v>
+        <v>0.1243062307615458</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.9496403258584112</v>
+        <v>0.9552585251016774</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.943295443669858</v>
+        <v>0.9502528598985412</v>
       </c>
     </row>
     <row r="8">
@@ -903,31 +903,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.1130553611466787</v>
+        <v>0.1067524592637853</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1475525568517657</v>
+        <v>0.1256611419430704</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.9339747920583513</v>
+        <v>0.9411919397898574</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.929240986273544</v>
+        <v>0.9491624834174684</v>
       </c>
     </row>
     <row r="9">
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.08644156572835811</v>
+        <v>0.09362189940972297</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.08993266734863439</v>
+        <v>0.09082323347729131</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.1316387905928806</v>
+        <v>0.140311486909253</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1367411964913371</v>
+        <v>0.1344493918707149</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.9104851225072262</v>
+        <v>0.8984061237338623</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.9392303068887573</v>
+        <v>0.9418030791104181</v>
       </c>
     </row>
     <row r="10">
@@ -987,31 +987,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.1676992579709667</v>
+        <v>0.1624719190570655</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.1556385889932825</v>
+        <v>0.155824486192658</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.2048689795133873</v>
+        <v>0.2000267600325709</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.2636764124918228</v>
+        <v>0.2633725207490659</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.7831897238180661</v>
+        <v>0.7935298478002494</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.7740403704111198</v>
+        <v>0.7766822498546533</v>
       </c>
     </row>
     <row r="11">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>36</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.4141826062838261</v>
+        <v>0.4093230600386596</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.439450306804493</v>
+        <v>0.4411695500269115</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.5734982786765774</v>
+        <v>0.5670684514600196</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6591727647977241</v>
+        <v>0.6588441613902175</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.6989934001093221</v>
+        <v>-0.6594036822747582</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-0.4121694181840581</v>
+        <v>-0.3974868379381513</v>
       </c>
     </row>
   </sheetData>
@@ -1080,8 +1080,8 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.803258550386407</v>
+        <v>1.811640014959316</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.19519374251454</v>
+        <v>11.73433813232548</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.192991347077931</v>
+        <v>3.425542020224752</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5483560774539995</v>
+        <v>0.5656778759592624</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0415754999849014</v>
+        <v>0.03976129996590316</v>
       </c>
     </row>
     <row r="3">
@@ -1175,19 +1175,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.183813131662352</v>
+        <v>2.144650564526655</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.178054346840753</v>
+        <v>7.942309918385686</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2.859729768149563</v>
+        <v>2.818210410594938</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.3677769274720452</v>
+        <v>0.3860016861454556</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0415754999849014</v>
+        <v>0.03976129996590316</v>
       </c>
     </row>
     <row r="4">
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.016382522837747</v>
+        <v>0.9153392344643816</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.198751157232222</v>
+        <v>1.600602232855568</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.482818652847415</v>
+        <v>1.265149095109176</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9025960052908232</v>
+        <v>0.9407570368538196</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.01560559996869415</v>
+        <v>0.01739350007846951</v>
       </c>
     </row>
     <row r="5">
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.291880340150533</v>
+        <v>1.203703904230022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.252964281494056</v>
+        <v>3.051959379974592</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.803597594114069</v>
+        <v>1.746985798446739</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7485222052034487</v>
+        <v>0.7640613458158985</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.01560559996869415</v>
+        <v>0.01739350007846951</v>
       </c>
     </row>
     <row r="6">
@@ -1271,19 +1271,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.4121053383088759</v>
+        <v>0.4714602776900032</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.543537563615988</v>
+        <v>1.897820551859945</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.24239187200174</v>
+        <v>1.377614079435872</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.931621764388689</v>
+        <v>0.9297561188507677</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3563357999664731</v>
+        <v>0.2664170998614281</v>
       </c>
     </row>
     <row r="7">
@@ -1303,19 +1303,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.5411509080732965</v>
+        <v>0.5372977600121799</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.898337973621847</v>
+        <v>2.008364718787072</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.377801862976621</v>
+        <v>1.417167851310166</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.8532446697614168</v>
+        <v>0.8447388022361562</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3563357999664731</v>
+        <v>0.2664170998614281</v>
       </c>
     </row>
     <row r="8">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.882214625020896</v>
+        <v>4.161693949436327</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.970333632921312</v>
+        <v>2.040023026692671</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8280190954980876</v>
+        <v>0.8459635528358119</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.259444999974221</v>
+        <v>0.2766284998506308</v>
       </c>
     </row>
     <row r="9">
@@ -1367,19 +1367,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6.777281158530899</v>
+        <v>6.847774932116176</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.603321178520027</v>
+        <v>2.616825353766693</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.4760668814719413</v>
+        <v>0.4706172001369925</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.259444999974221</v>
+        <v>0.2766284998506308</v>
       </c>
     </row>
     <row r="10">
@@ -1399,19 +1399,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.8001670285930573</v>
+        <v>0.4679830080978444</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.739824002654845</v>
+        <v>0.7839186945214357</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.933862457015711</v>
+        <v>0.8853918310677119</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8343269559314792</v>
+        <v>0.9709848797060088</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.757656599977054</v>
+        <v>1.806865000165999</v>
       </c>
     </row>
     <row r="11">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.384349764656433</v>
+        <v>0.4451622102221809</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.504528496213878</v>
+        <v>0.5531915763788861</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.91625247470343</v>
+        <v>0.7437684964953046</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.3425381015773061</v>
+        <v>0.9572342682890155</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.757656599977054</v>
+        <v>1.806865000165999</v>
       </c>
     </row>
     <row r="12">
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.1676992579709667</v>
+        <v>0.1624719190570655</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.04197129876685669</v>
+        <v>0.04001070472912769</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.2048689795133873</v>
+        <v>0.2000267600325709</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.7831897238180661</v>
+        <v>0.7935298478002494</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.008350399963092059</v>
+        <v>0.00704489997588098</v>
       </c>
     </row>
     <row r="13">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.1556385889932825</v>
+        <v>0.155824486192658</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06952525050455788</v>
+        <v>0.06936508468571714</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.2636764124918228</v>
+        <v>0.2633725207490659</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.7740403704111198</v>
+        <v>0.7766822498546533</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.008350399963092059</v>
+        <v>0.00704489997588098</v>
       </c>
     </row>
     <row r="14">
@@ -1527,19 +1527,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.08644156572835811</v>
+        <v>0.09362189940972297</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.01732877118875627</v>
+        <v>0.01968731335868546</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.1316387905928806</v>
+        <v>0.140311486909253</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9104851225072262</v>
+        <v>0.8984061237338623</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.01134580001235008</v>
+        <v>0.008847300196066499</v>
       </c>
     </row>
     <row r="15">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.08993266734863439</v>
+        <v>0.09082323347729131</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.01869815481788245</v>
+        <v>0.01807663897440507</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.1367411964913371</v>
+        <v>0.1344493918707149</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.9392303068887573</v>
+        <v>0.9418030791104181</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.01134580001235008</v>
+        <v>0.008847300196066499</v>
       </c>
     </row>
     <row r="16">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.06930430702866408</v>
+        <v>0.06423845125828263</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.009748896438029141</v>
+        <v>0.008670202071486763</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.09873650002926547</v>
+        <v>0.09311391985888448</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.9496403258584112</v>
+        <v>0.9552585251016774</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.2866834999877028</v>
+        <v>0.2378342999145389</v>
       </c>
     </row>
     <row r="17">
@@ -1623,19 +1623,19 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.07015926528444973</v>
+        <v>0.06320285787391408</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.01744735770179785</v>
+        <v>0.01545203900614268</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.1320884465114109</v>
+        <v>0.1243062307615458</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.943295443669858</v>
+        <v>0.9502528598985412</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.2866834999877028</v>
+        <v>0.2378342999145389</v>
       </c>
     </row>
     <row r="18">
@@ -1655,19 +1655,19 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.01278151468400596</v>
+        <v>0.01139608755886615</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.1130553611466787</v>
+        <v>0.1067524592637853</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.9339747920583513</v>
+        <v>0.9411919397898574</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.04229249997297302</v>
+        <v>0.03546379995532334</v>
       </c>
     </row>
     <row r="19">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.02177175703349356</v>
+        <v>0.01579072259443649</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.1475525568517657</v>
+        <v>0.1256611419430704</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.929240986273544</v>
+        <v>0.9491624834174684</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.04229249997297302</v>
+        <v>0.03546379995532334</v>
       </c>
     </row>
     <row r="20">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.4141826062838261</v>
+        <v>0.4093230600386596</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.3289002756449972</v>
+        <v>0.3215666286412646</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.5734982786765774</v>
+        <v>0.5670684514600196</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.6989934001093221</v>
+        <v>-0.6594036822747582</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3011837000376545</v>
+        <v>0.2732076998800039</v>
       </c>
     </row>
     <row r="21">
@@ -1751,19 +1751,19 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.439450306804493</v>
+        <v>0.4411695500269115</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.4345087338510758</v>
+        <v>0.434075628997979</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.6591727647977241</v>
+        <v>0.6588441613902175</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.4121694181840581</v>
+        <v>-0.3974868379381513</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.3011837000376545</v>
+        <v>0.2732076998800039</v>
       </c>
     </row>
   </sheetData>
@@ -1853,19 +1853,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4577423245416667</v>
+        <v>0.427152732383333</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4676129817962646</v>
+        <v>0.4461008906364441</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.02350202468085555</v>
+        <v>0.02522648143571526</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="3">
@@ -1888,16 +1888,16 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7767107091100001</v>
+        <v>0.8100440424433331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7913790941238403</v>
+        <v>0.8298920392990112</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.03298041959916442</v>
+        <v>0.03798975500867732</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="4">
@@ -1917,19 +1917,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.268330017933335</v>
+        <v>12.23588259858333</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11.66829681396484</v>
+        <v>14.52323055267334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.121975592436858</v>
+        <v>4.884577103339529</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="5">
@@ -1952,16 +1952,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.7078300066</v>
+        <v>0.7411633399333331</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6002568006515503</v>
+        <v>0.6023328900337219</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1075732059484497</v>
+        <v>0.1388304498996111</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="6">
@@ -1981,19 +1981,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.6878265418833333</v>
+        <v>0.491788586308333</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6979305744171143</v>
+        <v>0.4894126951694489</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04681373971987406</v>
+        <v>0.04193874171239098</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="7">
@@ -2013,19 +2013,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4251784799142856</v>
+        <v>0.355943428753333</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4235210716724396</v>
+        <v>0.363566666841507</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0097833659722155</v>
+        <v>0.01439259038679098</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6143005060203871</v>
+        <v>0.6043829160730932</v>
       </c>
     </row>
     <row r="8">
@@ -2048,16 +2048,16 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7308054723500002</v>
+        <v>0.764138805683333</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7281265258789062</v>
+        <v>0.754638671875</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.03960102183967695</v>
+        <v>0.04285373919556403</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="9">
@@ -2080,16 +2080,16 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8515116551800002</v>
+        <v>0.884844988513333</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8481852412223816</v>
+        <v>0.8820131421089172</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.01845002839822239</v>
+        <v>0.02399204103492103</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="10">
@@ -2112,16 +2112,16 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.5007143749</v>
+        <v>6.534047708233333</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9.30787467956543</v>
+        <v>9.273618698120117</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3.89673465177221</v>
+        <v>3.990921020214928</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="11">
@@ -2144,16 +2144,16 @@
         <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.7225611480857143</v>
+        <v>0.7558944814190474</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.7303330302238464</v>
+        <v>0.7683060765266418</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.04930144618875342</v>
+        <v>0.05144788662890289</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="12">
@@ -2176,16 +2176,16 @@
         <v>9</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7315574591444445</v>
+        <v>0.7648907924777775</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.7830245494842529</v>
+        <v>0.8257668614387512</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.07852184859614073</v>
+        <v>0.09228805911687046</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="13">
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.5562776856625</v>
+        <v>0.589611018995833</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.5541123151779175</v>
+        <v>0.5893903970718384</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.03468875873970756</v>
+        <v>0.02682217547185978</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6889598968104487</v>
+        <v>0.7075913077162266</v>
       </c>
     </row>
     <row r="14">
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5388745783714286</v>
+        <v>0.7234262850833331</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.5104673504829407</v>
+        <v>0.6857548356056213</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.04133443894466161</v>
+        <v>0.05726264144059373</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
     </row>
     <row r="15">
@@ -2272,16 +2272,16 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.6134066621750001</v>
+        <v>0.6551411973583331</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.655387818813324</v>
+        <v>0.686906099319458</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.06701995314928014</v>
+        <v>0.06094022918787374</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
     </row>
     <row r="16">
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.6020482167900001</v>
+        <v>0.464753391045833</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.5834084749221802</v>
+        <v>0.4640334844589233</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.04456171697357558</v>
+        <v>0.01771616346663128</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
     </row>
     <row r="17">
@@ -2336,16 +2336,16 @@
         <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.8976364834125001</v>
+        <v>0.9309698167458329</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.8737155199050903</v>
+        <v>0.9209719896316528</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.1499148134720184</v>
+        <v>0.1429209795427181</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
     </row>
     <row r="18">
@@ -2365,19 +2365,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.8590808631571427</v>
+        <v>0.934614251093333</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.8468930125236511</v>
+        <v>0.9407361745834351</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0585304521016713</v>
+        <v>0.02421529498274992</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.0725574924287043</v>
+        <v>0.06479258970697982</v>
       </c>
     </row>
     <row r="19">
@@ -2400,16 +2400,16 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.711419914675</v>
+        <v>0.744753248008333</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.6849434971809387</v>
+        <v>0.7170397043228149</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.03894572446789113</v>
+        <v>0.03847763498299236</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
     </row>
     <row r="20">
@@ -2432,16 +2432,16 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.8372134083222222</v>
+        <v>0.8818204444999996</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.839884877204895</v>
+        <v>0.8761746287345886</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.06802366816592559</v>
+        <v>0.04792121850924701</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
     </row>
     <row r="21">
@@ -2464,16 +2464,16 @@
         <v>4</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.78396485455</v>
+        <v>0.825668387108333</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8396415710449219</v>
+        <v>0.8470979332923889</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.1062883066172982</v>
+        <v>0.07831079624559706</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
     </row>
     <row r="22">
@@ -2496,16 +2496,16 @@
         <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.7945481076111112</v>
+        <v>0.8278814409444442</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.7897301316261292</v>
+        <v>0.8258500695228577</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.1713453209514227</v>
+        <v>0.1480645412099942</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
     </row>
     <row r="23">
@@ -2528,16 +2528,16 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.21171184602</v>
+        <v>0.245045179353333</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.2357701808214188</v>
+        <v>0.2684891223907471</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.02491101996407135</v>
+        <v>0.0234439554550484</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.08445850122369121</v>
+        <v>0.07015555097360522</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2565,9 +2565,9 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2653,13 +2653,13 @@
         <v>13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3420695592</v>
+        <v>0.375402892533333</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.361151784658432</v>
+        <v>0.3956413269042969</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.01908222545843202</v>
+        <v>0.0202384343709639</v>
       </c>
     </row>
     <row r="3">
@@ -2693,13 +2693,13 @@
         <v>66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7078300066</v>
+        <v>0.7411633399333331</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.6002568006515503</v>
+        <v>0.6023328900337219</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.1075732059484497</v>
+        <v>0.1388304498996111</v>
       </c>
     </row>
     <row r="4">
@@ -2733,13 +2733,13 @@
         <v>66</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6799995993</v>
+        <v>0.713332932633333</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.6492407321929932</v>
+        <v>0.6953516602516174</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.03075886710700682</v>
+        <v>0.01798127238171554</v>
       </c>
     </row>
     <row r="5">
@@ -2773,13 +2773,13 @@
         <v>11</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6164195438</v>
+        <v>0.649752877133333</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5551312565803528</v>
+        <v>0.5995945334434509</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.06128828721964719</v>
+        <v>0.05015834368988203</v>
       </c>
     </row>
     <row r="6">
@@ -2813,13 +2813,13 @@
         <v>13</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4223322092</v>
+        <v>0.455665542533333</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.4560461640357971</v>
+        <v>0.4246326088905334</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03371395483579714</v>
+        <v>0.03103293364279958</v>
       </c>
     </row>
     <row r="7">
@@ -2853,13 +2853,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6902810918</v>
+        <v>0.723614425133333</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.6888149976730347</v>
+        <v>0.7316637635231018</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.001466094126965301</v>
+        <v>0.008049338389768845</v>
       </c>
     </row>
     <row r="8">
@@ -2893,13 +2893,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7154300706</v>
+        <v>0.748763403933333</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.7683135867118835</v>
+        <v>0.8004918098449707</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.05288351611188358</v>
+        <v>0.05172840591163774</v>
       </c>
     </row>
     <row r="9">
@@ -2933,13 +2933,13 @@
         <v>13</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.527196523</v>
+        <v>2.560529856333333</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3.94652533531189</v>
+        <v>3.986841440200806</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.419328812311889</v>
+        <v>1.426311583867473</v>
       </c>
     </row>
     <row r="10">
@@ -2973,13 +2973,13 @@
         <v>13</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.1991687505</v>
+        <v>0.232502083833333</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.204454779624939</v>
+        <v>0.2415545880794525</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.005286029124938973</v>
+        <v>0.009052504246119503</v>
       </c>
     </row>
     <row r="11">
@@ -3013,13 +3013,13 @@
         <v>59</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.1713203375</v>
+        <v>0.204653670833333</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.1891121119260788</v>
+        <v>0.2232586592435837</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.01779177442607879</v>
+        <v>0.01860498841025068</v>
       </c>
     </row>
     <row r="12">
@@ -3053,13 +3053,13 @@
         <v>11</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.532671148</v>
+        <v>1.566004481333333</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.569715023040771</v>
+        <v>1.611940383911133</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.03704387504077156</v>
+        <v>0.04593590257779989</v>
       </c>
     </row>
     <row r="13">
@@ -3093,13 +3093,13 @@
         <v>11</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>24.66606415</v>
+        <v>24.69939748333333</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.36053085327148</v>
+        <v>34.96542358398438</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.694466703271484</v>
+        <v>10.26602610065104</v>
       </c>
     </row>
     <row r="14">
@@ -3133,13 +3133,13 @@
         <v>2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7160594243</v>
+        <v>0.749392757633333</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.7841199636459351</v>
+        <v>0.8349083065986633</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.06806053934593503</v>
+        <v>0.08551554896533031</v>
       </c>
     </row>
     <row r="15">
@@ -3173,13 +3173,13 @@
         <v>2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.2574832286</v>
+        <v>0.290816561933333</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.2749027907848358</v>
+        <v>0.3111718893051147</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.01741956218483581</v>
+        <v>0.02035532737178175</v>
       </c>
     </row>
     <row r="16">
@@ -3213,13 +3213,13 @@
         <v>13</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.1189453169</v>
+        <v>0.152278650233333</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.1135545670986176</v>
+        <v>0.1459822207689285</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.005390749801382447</v>
+        <v>0.006296429464404479</v>
       </c>
     </row>
     <row r="17">
@@ -3253,13 +3253,13 @@
         <v>13</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.4186509725</v>
+        <v>0.451984305833333</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.4245245456695557</v>
+        <v>0.4482038021087646</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.005873573169555668</v>
+        <v>0.00378050372456834</v>
       </c>
     </row>
     <row r="18">
@@ -3293,13 +3293,13 @@
         <v>13</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.4035592336</v>
+        <v>0.436892566933333</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.3848603069782257</v>
+        <v>0.4199692010879517</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.0186989266217743</v>
+        <v>0.01692336584538134</v>
       </c>
     </row>
     <row r="19">
@@ -3333,13 +3333,13 @@
         <v>13</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.285645288</v>
+        <v>1.318978621333333</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3.943996667861938</v>
+        <v>3.970489978790283</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.658351379861938</v>
+        <v>2.65151135745695</v>
       </c>
     </row>
     <row r="20">
@@ -3373,13 +3373,13 @@
         <v>13</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.1748821436</v>
+        <v>0.208215476933333</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.223762646317482</v>
+        <v>0.2602986395359039</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.04888050271748198</v>
+        <v>0.05208316260257093</v>
       </c>
     </row>
     <row r="21">
@@ -3413,13 +3413,13 @@
         <v>66</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.6216843355</v>
+        <v>0.655017668833333</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.6700734496116638</v>
+        <v>0.702951192855835</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.0483891141116638</v>
+        <v>0.04793352402250195</v>
       </c>
     </row>
     <row r="22">
@@ -3453,13 +3453,13 @@
         <v>2</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.9563964481</v>
+        <v>0.989729781433333</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.9803094863891602</v>
+        <v>1.035622239112854</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.02391303828916014</v>
+        <v>0.04589245767952099</v>
       </c>
     </row>
     <row r="23">
@@ -3493,13 +3493,13 @@
         <v>59</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.3472095897</v>
+        <v>0.380542923033333</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.3183821737766266</v>
+        <v>0.3667284548282623</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.0288274159233734</v>
+        <v>0.01381446820507065</v>
       </c>
     </row>
     <row r="24">
@@ -3533,13 +3533,13 @@
         <v>66</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>20.3312911</v>
+        <v>20.36462443333333</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.16526508331299</v>
+        <v>15.17016506195068</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.166026016687013</v>
+        <v>5.194459371382649</v>
       </c>
     </row>
     <row r="25">
@@ -3573,13 +3573,13 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.7383669957</v>
+        <v>0.771700329033333</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.7472752928733826</v>
+        <v>0.769953191280365</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.008908297173382596</v>
+        <v>0.001747137752967975</v>
       </c>
     </row>
     <row r="26">
@@ -3613,13 +3613,13 @@
         <v>66</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.8718019365</v>
+        <v>0.905135269833333</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.8838329911231995</v>
+        <v>0.9342366456985474</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.01203105462319942</v>
+        <v>0.02910137586521433</v>
       </c>
     </row>
     <row r="27">
@@ -3653,13 +3653,13 @@
         <v>77</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.1629232988</v>
+        <v>0.196256632133333</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.1824458539485931</v>
+        <v>0.2251373827457428</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.01952255514859313</v>
+        <v>0.0288807506124098</v>
       </c>
     </row>
     <row r="28">
@@ -3693,13 +3693,13 @@
         <v>13</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.1571181024</v>
+        <v>0.190451435733333</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.156172126531601</v>
+        <v>0.1995084285736084</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.0009459758683990349</v>
+        <v>0.009056992840275391</v>
       </c>
     </row>
     <row r="29">
@@ -3733,13 +3733,13 @@
         <v>59</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.352997271</v>
+        <v>0.386330604333333</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.3800654709339142</v>
+        <v>0.3304814100265503</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.02706819993391418</v>
+        <v>0.0558491943067827</v>
       </c>
     </row>
     <row r="30">
@@ -3773,13 +3773,13 @@
         <v>2</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.123204987</v>
+        <v>1.156538320333333</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1.15908682346344</v>
+        <v>1.200211405754089</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.0358818364634399</v>
+        <v>0.04367308542075632</v>
       </c>
     </row>
     <row r="31">
@@ -3813,13 +3813,13 @@
         <v>66</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.092741083</v>
+        <v>1.126074416333333</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1.091296792030334</v>
+        <v>1.103119134902954</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.001444290969665474</v>
+        <v>0.02295528143037884</v>
       </c>
     </row>
     <row r="32">
@@ -3853,13 +3853,13 @@
         <v>2</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.320124536</v>
+        <v>0.353457869333333</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.4211873710155487</v>
+        <v>0.4325835704803467</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1010628350155487</v>
+        <v>0.07912570114701367</v>
       </c>
     </row>
     <row r="33">
@@ -3893,13 +3893,13 @@
         <v>13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.2936576241</v>
+        <v>0.326990957433333</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.2836671471595764</v>
+        <v>0.3198771476745605</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.009990476940423598</v>
+        <v>0.00711380975877246</v>
       </c>
     </row>
     <row r="34">
@@ -3933,13 +3933,13 @@
         <v>66</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.2255152195</v>
+        <v>0.258848552833333</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.2403184175491333</v>
+        <v>0.2881537079811096</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.0148031980491333</v>
+        <v>0.0293051551477766</v>
       </c>
     </row>
     <row r="35">
@@ -3973,13 +3973,13 @@
         <v>66</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.4291585139</v>
+        <v>0.462491847233333</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.4545234441757202</v>
+        <v>0.4821867346763611</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.02536493027572023</v>
+        <v>0.01969488744302811</v>
       </c>
     </row>
     <row r="36">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4006,20 +4006,20 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.30870052</v>
+        <v>1.587747712333333</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.273052215576172</v>
+        <v>1.556389093399048</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.03564830442382805</v>
+        <v>0.03135861893428515</v>
       </c>
     </row>
     <row r="37">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4046,20 +4046,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.518584403</v>
+        <v>0.715870373433333</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.460506439208984</v>
+        <v>0.6864585876464844</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.0580779637910156</v>
+        <v>0.02941178578684867</v>
       </c>
     </row>
     <row r="38">
@@ -4070,19 +4070,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.093338499</v>
+        <v>0.911940160533333</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.096970677375793</v>
+        <v>0.9961535334587097</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.003632178375793549</v>
+        <v>0.08421337292537667</v>
       </c>
     </row>
     <row r="39">
@@ -4110,36 +4110,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.4489249546</v>
+        <v>1.171096652333333</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.4767597019672394</v>
+        <v>1.137853622436523</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.0278347473672394</v>
+        <v>0.03324302989680961</v>
       </c>
     </row>
     <row r="40">
@@ -4150,19 +4150,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4173,13 +4173,13 @@
         <v>11</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.2698603833</v>
+        <v>1.357867616333333</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.2509285807609558</v>
+        <v>1.410189151763916</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.0189318025390442</v>
+        <v>0.05232153543058304</v>
       </c>
     </row>
     <row r="41">
@@ -4190,11 +4190,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4206,20 +4206,20 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.7745538364</v>
+        <v>0.348147133133333</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.7225026488304138</v>
+        <v>0.3404200375080109</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.05205118756958615</v>
+        <v>0.007727095625322145</v>
       </c>
     </row>
     <row r="42">
@@ -4230,36 +4230,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.246013384</v>
+        <v>0.269104737733333</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.2570747435092926</v>
+        <v>0.2696838974952698</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.0110613595092926</v>
+        <v>0.0005791597619367872</v>
       </c>
     </row>
     <row r="43">
@@ -4270,36 +4270,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>6.350858092</v>
+        <v>0.457944805633333</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.11670398712158</v>
+        <v>0.4240674078464508</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.765845895121582</v>
+        <v>0.0338773977868822</v>
       </c>
     </row>
     <row r="44">
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4322,24 +4322,24 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.554414379</v>
+        <v>0.201254462533333</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.5361248254776</v>
+        <v>0.2408322542905807</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.01828955352239992</v>
+        <v>0.03957779175724774</v>
       </c>
     </row>
     <row r="45">
@@ -4354,15 +4354,15 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4373,13 +4373,13 @@
         <v>13</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.6825370401</v>
+        <v>0.279330841733333</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.6072922348976135</v>
+        <v>0.3091118335723877</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.07524480520238652</v>
+        <v>0.02978099183905469</v>
       </c>
     </row>
     <row r="46">
@@ -4394,32 +4394,32 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.8786068272000001</v>
+        <v>0.508504715633333</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.977863609790802</v>
+        <v>0.5171422958374023</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.09925678259080195</v>
+        <v>0.008637580204069351</v>
       </c>
     </row>
     <row r="47">
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4453,13 +4453,13 @@
         <v>66</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1.137763319</v>
+        <v>0.628326891133333</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1.118329286575317</v>
+        <v>0.60321044921875</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.01943403242468267</v>
+        <v>0.02511644191458295</v>
       </c>
     </row>
     <row r="48">
@@ -4474,32 +4474,32 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.324534283</v>
+        <v>0.391863733733333</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1.350028872489929</v>
+        <v>0.3840939402580261</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.02549458948992922</v>
+        <v>0.007769793475306874</v>
       </c>
     </row>
     <row r="49">
@@ -4514,32 +4514,32 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.3148137998</v>
+        <v>1.359527666333333</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.297760933637619</v>
+        <v>1.454799652099609</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.017052866162381</v>
+        <v>0.09527198576627627</v>
       </c>
     </row>
     <row r="50">
@@ -4554,15 +4554,15 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4573,13 +4573,13 @@
         <v>77</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.2357714044</v>
+        <v>0.238985266733333</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.2361073642969131</v>
+        <v>0.2627172768115997</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.0003359598969131516</v>
+        <v>0.02373201007826672</v>
       </c>
     </row>
     <row r="51">
@@ -4594,32 +4594,32 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.4246114723</v>
+        <v>2.227883409333333</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.3842235207557678</v>
+        <v>3.973539113998413</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.04038795154423219</v>
+        <v>1.74565570466508</v>
       </c>
     </row>
     <row r="52">
@@ -4634,15 +4634,15 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4653,13 +4653,13 @@
         <v>77</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.1679211292</v>
+        <v>0.445717419733333</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.2221300303936005</v>
+        <v>0.4641921818256378</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.05420890119360047</v>
+        <v>0.01847476209230481</v>
       </c>
     </row>
     <row r="53">
@@ -4674,11 +4674,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -4686,20 +4686,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.2459975084</v>
+        <v>1.082712658333333</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.2745456099510193</v>
+        <v>1.04656457901001</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.02854810155101928</v>
+        <v>0.03614807932332331</v>
       </c>
     </row>
     <row r="54">
@@ -4714,11 +4714,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
@@ -4726,20 +4726,20 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.4751713823</v>
+        <v>2.242157719333333</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.4716583788394928</v>
+        <v>2.540665149688721</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.003513003460507202</v>
+        <v>0.2985074303553876</v>
       </c>
     </row>
     <row r="55">
@@ -4754,15 +4754,15 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4773,13 +4773,13 @@
         <v>66</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.5949935578</v>
+        <v>15.89243177333333</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.5799311399459839</v>
+        <v>11.51270484924316</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.01506241785401607</v>
+        <v>4.379726924090168</v>
       </c>
     </row>
     <row r="56">
@@ -4794,32 +4794,32 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.3585304004</v>
+        <v>0.5744449914333331</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.3259930610656738</v>
+        <v>3.965265274047852</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.03253733933432618</v>
+        <v>3.390820282614519</v>
       </c>
     </row>
     <row r="57">
@@ -4834,15 +4834,15 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.326194333</v>
+        <v>0.985308700033333</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1.411110281944275</v>
+        <v>0.9471846222877502</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.08491594894427501</v>
+        <v>0.0381240777455828</v>
       </c>
     </row>
     <row r="58">
@@ -4874,15 +4874,15 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4893,13 +4893,13 @@
         <v>77</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.2056519334</v>
+        <v>0.286855816233333</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.2370087206363678</v>
+        <v>0.3013995885848999</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.03135678723636781</v>
+        <v>0.0145437723515669</v>
       </c>
     </row>
     <row r="59">
@@ -4914,15 +4914,15 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>66</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>2.194550076</v>
+        <v>0.520585244233333</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3.765689849853516</v>
+        <v>0.4467231929302216</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.571139773853516</v>
+        <v>0.07386205130311141</v>
       </c>
     </row>
     <row r="60">
@@ -4954,32 +4954,32 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.4123840864</v>
+        <v>0.641169872433333</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.4445462822914124</v>
+        <v>0.5784047245979309</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.03216219589141234</v>
+        <v>0.0627651478354021</v>
       </c>
     </row>
     <row r="61">
@@ -4994,32 +4994,32 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.049379325</v>
+        <v>0.234141533933333</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1.01793110370636</v>
+        <v>0.2235834747552872</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.03144822129364022</v>
+        <v>0.01055805917804584</v>
       </c>
     </row>
     <row r="62">
@@ -5034,15 +5034,15 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5050,16 +5050,16 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>2.208824386</v>
+        <v>1.211780883333333</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2.355108261108398</v>
+        <v>1.122225880622864</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1462838751083986</v>
+        <v>0.08955500271046923</v>
       </c>
     </row>
     <row r="63">
@@ -5074,32 +5074,32 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>15.85909844</v>
+        <v>0.311755190933333</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.04558944702148</v>
+        <v>0.3341097235679626</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3.813508992978516</v>
+        <v>0.02235453263462966</v>
       </c>
     </row>
     <row r="64">
@@ -5114,15 +5114,15 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5133,13 +5133,13 @@
         <v>13</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.5411116580999999</v>
+        <v>0.262351850833333</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3.939569711685181</v>
+        <v>0.299102783203125</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3.39845805358518</v>
+        <v>0.03675093236979199</v>
       </c>
     </row>
     <row r="65">
@@ -5154,32 +5154,32 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.9519753667</v>
+        <v>0.512177928533333</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.9018548727035522</v>
+        <v>0.4711389541625977</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.0501204939964478</v>
+        <v>0.04103897437073534</v>
       </c>
     </row>
     <row r="66">
@@ -5194,32 +5194,32 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.2535224829</v>
+        <v>1.007360776833333</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.2774220407009125</v>
+        <v>1.078540325164795</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.02389955780091246</v>
+        <v>0.07117954833146189</v>
       </c>
     </row>
     <row r="67">
@@ -5234,32 +5234,32 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.4872519109</v>
+        <v>0.436121404133333</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.4231140911579132</v>
+        <v>0.4254132509231567</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.06413781974208677</v>
+        <v>0.01070815321017626</v>
       </c>
     </row>
     <row r="68">
@@ -5274,32 +5274,32 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.6078365391</v>
+        <v>2.139302289333333</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.5301340222358704</v>
+        <v>2.82478928565979</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.07770251686412966</v>
+        <v>0.6854869963264569</v>
       </c>
     </row>
     <row r="69">
@@ -5314,32 +5314,32 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.2008082006</v>
+        <v>1.375822484333333</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.1975063532590866</v>
+        <v>1.357595205307007</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.003301847340913378</v>
+        <v>0.01822727902632626</v>
       </c>
     </row>
     <row r="70">
@@ -5354,32 +5354,32 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1.17844755</v>
+        <v>0.305085446033333</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1.101345419883728</v>
+        <v>0.3353050649166107</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.07710213011627198</v>
+        <v>0.03021961888327773</v>
       </c>
     </row>
     <row r="71">
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5402,24 +5402,24 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0.2784218576</v>
+        <v>1.644633234333333</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0.3097309470176697</v>
+        <v>1.711657524108887</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.03130908941766969</v>
+        <v>0.06702428977555375</v>
       </c>
     </row>
     <row r="72">
@@ -5434,32 +5434,32 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.2290185175</v>
+        <v>0.522691355633333</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0.2542190551757812</v>
+        <v>0.5145269632339478</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.02520053767578126</v>
+        <v>0.008164392399385267</v>
       </c>
     </row>
     <row r="73">
@@ -5474,15 +5474,15 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.4788445952</v>
+        <v>5.456903730333333</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.4526976943016052</v>
+        <v>7.305186748504639</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.02614690089839478</v>
+        <v>1.848283018171306</v>
       </c>
     </row>
     <row r="74">
@@ -5514,15 +5514,15 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι100</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5533,13 +5533,13 @@
         <v>11</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.9740274435</v>
+        <v>18.53542760333333</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1.047528147697449</v>
+        <v>34.33768844604492</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.0735007041974487</v>
+        <v>15.80226084271159</v>
       </c>
     </row>
     <row r="75">
@@ -5554,15 +5554,15 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5573,13 +5573,13 @@
         <v>77</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.4027880708</v>
+        <v>0.391807875633333</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0.4147665202617645</v>
+        <v>0.3391900360584259</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.01197844946176452</v>
+        <v>0.05261783957490712</v>
       </c>
     </row>
     <row r="76">
@@ -5594,15 +5594,15 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -5613,13 +5613,13 @@
         <v>59</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>2.105968956</v>
+        <v>0.258273094933333</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2.681771278381348</v>
+        <v>0.2637189030647278</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5758023223813478</v>
+        <v>0.00544580813139478</v>
       </c>
     </row>
     <row r="77">
@@ -5634,15 +5634,15 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5650,71 +5650,71 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1.342489151</v>
+        <v>1.707141332333333</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1.338168501853943</v>
+        <v>2.064854145050049</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.004320649146057232</v>
+        <v>0.3577128127167157</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.2717521127</v>
+        <v>0.862086998433333</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.2926404774188995</v>
+        <v>0.8037363290786743</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.02088836471889954</v>
+        <v>0.05835066935465871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -5730,119 +5730,119 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1.611299901</v>
+        <v>0.7411633399333331</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1.673943281173706</v>
+        <v>0.7140905857086182</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.06264338017370608</v>
+        <v>0.02707275422471489</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.4893580223</v>
+        <v>0.457642746133333</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.4493631720542908</v>
+        <v>0.4608457982540131</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.0399948502457092</v>
+        <v>0.003203052120680061</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>5.423570397</v>
+        <v>0.723614425133333</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.376374244689941</v>
+        <v>0.6982683539390564</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.952803847689942</v>
+        <v>0.02534607119427656</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Μέλι100</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5850,111 +5850,111 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>18.50209427</v>
+        <v>1.211780883333333</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>34.36826705932617</v>
+        <v>1.128574728965759</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>15.86617278932617</v>
+        <v>0.08320615436757373</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.3584745423</v>
+        <v>1.171096652333333</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4047405123710632</v>
+        <v>1.151209354400635</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.04626597007106326</v>
+        <v>0.01988729793269828</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>198</v>
+        <v>100</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.2249397616</v>
+        <v>0.376512968733333</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0.2529844343662262</v>
+        <v>0.3886425495147705</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.02804467276622619</v>
+        <v>0.0121295807814375</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mesos_oros.csv</t>
+          <t>mesos_oros_nomeli.csv</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5970,16 +5970,16 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1.673807999</v>
+        <v>1.102172150333333</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2.010146617889404</v>
+        <v>0.9358748197555542</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3363386188894042</v>
+        <v>0.1662973305777788</v>
       </c>
     </row>
     <row r="86">
@@ -5994,15 +5994,15 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.7951488577</v>
+        <v>1.357508922333333</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0.7580238580703735</v>
+        <v>1.376990556716919</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.03712499962962645</v>
+        <v>0.01948163438358597</v>
       </c>
     </row>
     <row r="87">
@@ -6034,32 +6034,32 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.6744008803</v>
+        <v>0.276579610433333</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0.6948463916778564</v>
+        <v>0.2834627330303192</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.02044551137785644</v>
+        <v>0.006883122596986202</v>
       </c>
     </row>
     <row r="88">
@@ -6074,15 +6074,15 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -6093,13 +6093,13 @@
         <v>77</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0.4243094128</v>
+        <v>0.332251750233333</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0.3865053355693817</v>
+        <v>0.3663086593151093</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.03780407723061829</v>
+        <v>0.03405690908177628</v>
       </c>
     </row>
     <row r="89">
@@ -6114,15 +6114,15 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -6133,13 +6133,13 @@
         <v>2</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>0.6902810918</v>
+        <v>1.156538320333333</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0.7064191102981567</v>
+        <v>1.256315588951111</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.01613801849815677</v>
+        <v>0.0997772686177778</v>
       </c>
     </row>
     <row r="90">
@@ -6154,32 +6154,32 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.17844755</v>
+        <v>0.353457869333333</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1.06498920917511</v>
+        <v>0.4342175126075745</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1134583408248901</v>
+        <v>0.08075964327424145</v>
       </c>
     </row>
     <row r="91">
@@ -6194,32 +6194,32 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1.137763319</v>
+        <v>0.771700329033333</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1.061428427696228</v>
+        <v>0.7103631496429443</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.07633489130377202</v>
+        <v>0.06133717939038863</v>
       </c>
     </row>
     <row r="92">
@@ -6234,15 +6234,15 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -6250,16 +6250,16 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.3431796354</v>
+        <v>0.518281239933333</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0.3544516265392303</v>
+        <v>0.5395135879516602</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.01127199113923033</v>
+        <v>0.02123234801832719</v>
       </c>
     </row>
     <row r="93">
@@ -6274,32 +6274,32 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.068838817</v>
+        <v>0.801613055833333</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0.8249011635780334</v>
+        <v>0.8140665292739868</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2439376534219666</v>
+        <v>0.01245347344065384</v>
       </c>
     </row>
     <row r="94">
@@ -6314,32 +6314,32 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1.324175589</v>
+        <v>0.207179274033333</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1.341570854187012</v>
+        <v>0.1901392638683319</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.01739526518701173</v>
+        <v>0.01704001016500109</v>
       </c>
     </row>
     <row r="95">
@@ -6354,15 +6354,15 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -6373,13 +6373,13 @@
         <v>13</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>0.2432462771</v>
+        <v>0.402302509033333</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0.2302937060594559</v>
+        <v>0.3726710677146912</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.01295257104054412</v>
+        <v>0.02963144131864182</v>
       </c>
     </row>
     <row r="96">
@@ -6394,15 +6394,15 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>0.2989184169</v>
+        <v>1.126671832333333</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0.3239804804325104</v>
+        <v>1.173476457595825</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.02506206353251039</v>
+        <v>0.04680462526249229</v>
       </c>
     </row>
     <row r="97">
@@ -6434,32 +6434,32 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>1.123204987</v>
+        <v>0.330485890633333</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1.290097832679749</v>
+        <v>0.3563388884067535</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1668928456797485</v>
+        <v>0.02585299777342054</v>
       </c>
     </row>
     <row r="98">
@@ -6474,11 +6474,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -6493,13 +6493,13 @@
         <v>2</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0.320124536</v>
+        <v>0.325359860233333</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0.3924970924854279</v>
+        <v>0.4041097164154053</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.07237255648542784</v>
+        <v>0.07874985618207225</v>
       </c>
     </row>
     <row r="99">
@@ -6514,15 +6514,15 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>0.7383669957</v>
+        <v>0.285044081233333</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0.6492184400558472</v>
+        <v>0.3029941022396088</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0891485556441528</v>
+        <v>0.01795002100627574</v>
       </c>
     </row>
     <row r="100">
@@ -6554,15 +6554,15 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -6570,16 +6570,16 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0.4849479066</v>
+        <v>0.294179423333333</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0.5044084787368774</v>
+        <v>0.3037362694740295</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.01946057213687746</v>
+        <v>0.009556846140696518</v>
       </c>
     </row>
     <row r="101">
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6602,24 +6602,24 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0.7682797225</v>
+        <v>0.401127344033333</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0.7981023788452148</v>
+        <v>0.4154733419418335</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.02982265634521486</v>
+        <v>0.0143459979085005</v>
       </c>
     </row>
     <row r="102">
@@ -6634,32 +6634,32 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>0.1738459407</v>
+        <v>1.551917736333333</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0.1555236130952835</v>
+        <v>1.402063131332397</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.0183223276047165</v>
+        <v>0.1498546050009355</v>
       </c>
     </row>
     <row r="103">
@@ -6674,32 +6674,32 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>0.3689691757</v>
+        <v>1.398407413333333</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0.3553385436534882</v>
+        <v>1.164221405982971</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.01363063204651183</v>
+        <v>0.2341860073503619</v>
       </c>
     </row>
     <row r="104">
@@ -6714,11 +6714,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1.093338499</v>
+        <v>1.707141332333333</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1.159862399101257</v>
+        <v>2.117724657058716</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.06652390010125742</v>
+        <v>0.4105833247253827</v>
       </c>
     </row>
     <row r="105">
@@ -6754,15 +6754,15 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>0.2635105088</v>
+        <v>0.878598935833333</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0.3176901936531067</v>
+        <v>0.7719368934631348</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.0541796848531067</v>
+        <v>0.1066620423701983</v>
       </c>
     </row>
     <row r="106">
@@ -6794,11 +6794,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>0.2920265269</v>
+        <v>0.230709953033333</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0.3431359231472015</v>
+        <v>0.2370027899742126</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.05110939624720151</v>
+        <v>0.006292836940879648</v>
       </c>
     </row>
     <row r="107">
@@ -6830,11 +6830,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6846,20 +6846,20 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>0.2517107479</v>
+        <v>0.905135269833333</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0.2695100903511047</v>
+        <v>0.8977960348129272</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.01779934245110476</v>
+        <v>0.007339235020405788</v>
       </c>
     </row>
     <row r="108">
@@ -6870,36 +6870,36 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>0.26084609</v>
+        <v>0.649752877133333</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0.2482682019472122</v>
+        <v>0.5459265112876892</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.01257788805278776</v>
+        <v>0.1038263658456438</v>
       </c>
     </row>
     <row r="109">
@@ -6910,36 +6910,36 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>0.3677940107</v>
+        <v>0.196256632133333</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0.3816839456558228</v>
+        <v>0.2024093717336655</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.01388993495582275</v>
+        <v>0.006152739600332469</v>
       </c>
     </row>
     <row r="110">
@@ -6950,19 +6950,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1.518584403</v>
+        <v>0.641169872433333</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1.395440936088562</v>
+        <v>0.5336463451385498</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.123143466911438</v>
+        <v>0.1075235272947832</v>
       </c>
     </row>
     <row r="111">
@@ -6990,19 +6990,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7013,13 +7013,13 @@
         <v>66</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1.36507408</v>
+        <v>0.245730351233333</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1.12596070766449</v>
+        <v>0.2857781648635864</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2391133723355103</v>
+        <v>0.04004781363025342</v>
       </c>
     </row>
     <row r="112">
@@ -7030,36 +7030,36 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1.673807999</v>
+        <v>0.238985266733333</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2.07517671585083</v>
+        <v>0.2649375200271606</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.40136871685083</v>
+        <v>0.02595225329382764</v>
       </c>
     </row>
     <row r="113">
@@ -7070,11 +7070,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -7093,13 +7093,13 @@
         <v>11</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>0.8452656025</v>
+        <v>1.342060896333333</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0.7371086478233337</v>
+        <v>1.268678426742554</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.1081569546766663</v>
+        <v>0.07338246959077921</v>
       </c>
     </row>
     <row r="114">
@@ -7110,19 +7110,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>0.1973766197</v>
+        <v>1.362724447333333</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0.2025487422943115</v>
+        <v>1.420007944107056</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.005172122594311518</v>
+        <v>0.05728349677372258</v>
       </c>
     </row>
     <row r="115">
@@ -7150,36 +7150,36 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>0.5949935578</v>
+        <v>0.218128504333333</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0.6571354269981384</v>
+        <v>0.2221398502588272</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.06214186919813847</v>
+        <v>0.004011345925494209</v>
       </c>
     </row>
     <row r="116">
@@ -7190,36 +7190,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>1.541170363</v>
+        <v>0.330306298733333</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1.32078218460083</v>
+        <v>0.3063076138496399</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2203881783991699</v>
+        <v>0.02399868488369311</v>
       </c>
     </row>
     <row r="117">
@@ -7230,15 +7230,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
@@ -7246,20 +7246,20 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>0.9121678955</v>
+        <v>0.336476286933333</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0.753566563129425</v>
+        <v>0.3302372395992279</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.1586013323705749</v>
+        <v>0.006239047334105075</v>
       </c>
     </row>
     <row r="118">
@@ -7270,19 +7270,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -7293,13 +7293,13 @@
         <v>77</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0.3251084991</v>
+        <v>0.238654327833333</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0.3110949993133545</v>
+        <v>0.2537119686603546</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.01401349978664551</v>
+        <v>0.0150576408270216</v>
       </c>
     </row>
     <row r="119">
@@ -7310,19 +7310,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -7330,16 +7330,16 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>0.2574832286</v>
+        <v>0.436121404133333</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0.2654684484004974</v>
+        <v>0.4208275973796844</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.007985219800497434</v>
+        <v>0.01529380675364855</v>
       </c>
     </row>
     <row r="120">
@@ -7350,36 +7350,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1.095022518</v>
+        <v>0.715870373433333</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1.069160342216492</v>
+        <v>0.5989795923233032</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.02586217578350825</v>
+        <v>0.1168907811100298</v>
       </c>
     </row>
     <row r="121">
@@ -7390,15 +7390,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
@@ -7406,20 +7406,20 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>0.4291585139</v>
+        <v>0.269104737733333</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0.4206913709640503</v>
+        <v>0.2605906426906586</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.00846714293594969</v>
+        <v>0.008514095042674419</v>
       </c>
     </row>
     <row r="122">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7442,24 +7442,24 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>0.8718019365</v>
+        <v>0.262351850833333</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0.7702234983444214</v>
+        <v>0.2645620703697205</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.1015784381555787</v>
+        <v>0.002210219536387448</v>
       </c>
     </row>
     <row r="123">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7482,24 +7482,24 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>0.5817890692</v>
+        <v>0.319769955033333</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0.515716016292572</v>
+        <v>0.3101177215576172</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.06607305290742793</v>
+        <v>0.00965223347571581</v>
       </c>
     </row>
     <row r="124">
@@ -7514,32 +7514,32 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>0.1629232988</v>
+        <v>0.348147133133333</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0.1605194211006165</v>
+        <v>0.361503005027771</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.00240387769938355</v>
+        <v>0.01335587189443799</v>
       </c>
     </row>
     <row r="125">
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7573,13 +7573,13 @@
         <v>11</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>0.6078365391</v>
+        <v>1.359527666333333</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0.5066133141517639</v>
+        <v>1.441036939620972</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1012232249482361</v>
+        <v>0.08150927328763857</v>
       </c>
     </row>
     <row r="126">
@@ -7594,32 +7594,32 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>0.2123970179</v>
+        <v>0.989729781433333</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0.2551884651184082</v>
+        <v>1.013107538223267</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.04279144721840819</v>
+        <v>0.02337775678993359</v>
       </c>
     </row>
     <row r="127">
@@ -7634,32 +7634,32 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι30</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>0.2056519334</v>
+        <v>0.965499722733333</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0.2321868240833282</v>
+        <v>1.083471059799194</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.02653489068332826</v>
+        <v>0.1179713370658614</v>
       </c>
     </row>
     <row r="128">
@@ -7674,15 +7674,15 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7693,13 +7693,13 @@
         <v>11</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>1.308727563</v>
+        <v>1.020474761133333</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1.259850859642029</v>
+        <v>1.217989087104797</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.04887670335797112</v>
+        <v>0.1975143259714645</v>
       </c>
     </row>
     <row r="129">
@@ -7714,11 +7714,11 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
@@ -7726,20 +7726,20 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>1.329391114</v>
+        <v>0.512177928533333</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1.320830225944519</v>
+        <v>0.4905913174152374</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.008560888055481053</v>
+        <v>0.02158661111809557</v>
       </c>
     </row>
     <row r="130">
@@ -7754,32 +7754,32 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>0.184795171</v>
+        <v>1.587747712333333</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0.1874556392431259</v>
+        <v>1.527432680130005</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.002660468243125907</v>
+        <v>0.06031503220332812</v>
       </c>
     </row>
     <row r="131">
@@ -7794,11 +7794,11 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
@@ -7806,20 +7806,20 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>0.2969729654</v>
+        <v>0.201254462533333</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0.2739227116107941</v>
+        <v>0.2108989804983139</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.02305025378920594</v>
+        <v>0.009644517964980892</v>
       </c>
     </row>
     <row r="132">
@@ -7834,32 +7834,32 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>0.3031429536</v>
+        <v>0.363291982933333</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0.3051880300045013</v>
+        <v>0.4028001725673676</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.002045076404501356</v>
+        <v>0.03950818963403457</v>
       </c>
     </row>
     <row r="133">
@@ -7874,32 +7874,32 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Νερό</t>
+          <t>Λάδι</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>0.2053209945</v>
+        <v>1.357867616333333</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0.2051668763160706</v>
+        <v>1.416437983512878</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.0001541181839294359</v>
+        <v>0.05857036717954545</v>
       </c>
     </row>
     <row r="134">
@@ -7914,32 +7914,32 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>0.4027880708</v>
+        <v>1.082712658333333</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0.388838142156601</v>
+        <v>0.9589844942092896</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.01394992864339906</v>
+        <v>0.1237281641240435</v>
       </c>
     </row>
     <row r="135">
@@ -7954,15 +7954,15 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Μέλι70</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -7973,13 +7973,13 @@
         <v>13</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>0.6825370401</v>
+        <v>0.117611357553333</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0.5594870448112488</v>
+        <v>0.1281883120536804</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.1230499952887513</v>
+        <v>0.01057695450034742</v>
       </c>
     </row>
     <row r="136">
@@ -7994,32 +7994,32 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>46</v>
+        <v>174</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Λάδι</t>
+          <t>Νερό</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>0.2357714044</v>
+        <v>0.308726424433333</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0.2216358631849289</v>
+        <v>0.3380468189716339</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.0141355412150711</v>
+        <v>0.02932039453830093</v>
       </c>
     </row>
     <row r="137">
@@ -8034,32 +8034,32 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Αλατόνερο</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>0.2290185175</v>
+        <v>0.358348238533333</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0.2439566403627396</v>
+        <v>0.4061658084392548</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.01493812286273957</v>
+        <v>0.04781756990592179</v>
       </c>
     </row>
     <row r="138">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8082,24 +8082,24 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>0.2864366217</v>
+        <v>0.985308700033333</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0.2695556581020355</v>
+        <v>0.8815433979034424</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.01688096359796448</v>
+        <v>0.1037653021298907</v>
       </c>
     </row>
     <row r="139">
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8122,24 +8122,24 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Σφαίρα</t>
+          <t>Κύβος</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0.3148137998</v>
+        <v>2.655901348333333</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0.3209652304649353</v>
+        <v>2.142945528030396</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.006151430664935287</v>
+        <v>0.5129558203029374</v>
       </c>
     </row>
     <row r="140">
@@ -8154,15 +8154,15 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Μέλι70</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -8173,13 +8173,13 @@
         <v>11</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>1.326194333</v>
+        <v>1.291578382333333</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1.45796000957489</v>
+        <v>1.686028242111206</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.1317656765748902</v>
+        <v>0.3944498597778729</v>
       </c>
     </row>
     <row r="141">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8202,24 +8202,24 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Κύβος</t>
+          <t>Δίσκος</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>0.9563964481</v>
+        <v>1.566004481333333</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0.9384536147117615</v>
+        <v>1.617012023925781</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.01794283338823854</v>
+        <v>0.05100754259244833</v>
       </c>
     </row>
     <row r="142">
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Μέλι30</t>
+          <t>Αλατόνερο</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
@@ -8246,624 +8246,24 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Δίσκος</t>
+          <t>Σφαίρα</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>0.8986855925</v>
+        <v>0.337777867133333</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1.088804841041565</v>
+        <v>0.3430270552635193</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.1901192485415649</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>121</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Μέλι70</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>0.9871414278</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>1.220675706863403</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>0.2335342790634033</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>144</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Μέλι70</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Σφαίρα</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>0.4788445952</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>0.4519012868404388</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>0.02694330835956116</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>31</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Αλατόνερο</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>1.554414379</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>1.546813607215881</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>0.007600771784118665</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>10</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Αλατόνερο</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Κύβος</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>0.1679211292</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>0.1763252019882202</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>0.008404072788220224</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>173</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Νερό</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Σφαίρα</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>0.3299586496</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>0.3871954679489136</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>0.05723681834891359</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>61</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Λάδι</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>1.291141002</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>1.467619180679321</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>0.1764781786793213</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>19</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Αλατόνερο</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>1.049379325</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>0.9567635059356689</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>0.09261581906433114</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>149</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Νερό</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Σφαίρα</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>0.08427802422</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>0.09080603718757629</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>0.006528012967576297</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>174</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Νερό</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Σφαίρα</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>0.2753930911</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>0.315744936466217</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>0.04035184536621705</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>110</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Μέλι70</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>0.3250149052</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>0.4643187522888184</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>0.1393038470888184</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>56</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Λάδι</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>0.9519753667</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>0.7954334616661072</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>0.1565419050338929</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>141</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Μέλι70</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Κύβος</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>2.622568015</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>2.00287652015686</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>0.6196914948431398</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>127</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Μέλι70</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>1.258245049</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>1.625967860221863</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>0.3677228112218629</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>67</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Λάδι</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Δίσκος</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>1.499231578</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>1.640881299972534</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>0.1416497219725341</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>mesos_oros_nomeli.csv</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>30</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Αλατόνερο</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Σφαίρα</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>0.3044445338</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>0.2934275567531586</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>0.0110169770468414</v>
+        <v>0.005249188130186266</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J157"/>
+  <autoFilter ref="A1:J142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8909,7 +8309,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8924,7 +8324,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -8939,7 +8339,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -8954,7 +8354,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -8969,7 +8369,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -8984,7 +8384,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -8999,7 +8399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -9014,7 +8414,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -9029,7 +8429,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -9044,7 +8444,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9059,7 +8459,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>207</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9074,7 +8474,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9089,7 +8489,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -9104,7 +8504,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9119,7 +8519,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9134,7 +8534,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9149,7 +8549,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9164,7 +8564,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -9179,7 +8579,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -9194,7 +8594,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -9209,7 +8609,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -9224,7 +8624,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -9239,7 +8639,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -9254,7 +8654,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -9269,7 +8669,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -9284,7 +8684,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>178</v>
+        <v>38</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -9299,7 +8699,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9314,7 +8714,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9329,7 +8729,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9344,7 +8744,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -9359,7 +8759,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -9374,7 +8774,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -9389,7 +8789,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -9404,7 +8804,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -9419,7 +8819,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -9434,7 +8834,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -9449,7 +8849,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -9464,7 +8864,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -9479,7 +8879,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -9494,7 +8894,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>206</v>
+        <v>90</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -9509,7 +8909,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -9524,7 +8924,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -9539,7 +8939,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>177</v>
+        <v>60</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -9554,7 +8954,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -9569,7 +8969,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -9584,7 +8984,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -9599,7 +8999,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -9614,7 +9014,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>111</v>
+        <v>206</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -9629,7 +9029,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -9644,7 +9044,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -9659,7 +9059,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -9674,7 +9074,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -9689,7 +9089,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -9704,7 +9104,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -9719,7 +9119,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -9734,7 +9134,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -9749,7 +9149,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -9764,7 +9164,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -9779,7 +9179,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -9794,7 +9194,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9809,7 +9209,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9824,7 +9224,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9839,7 +9239,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9854,7 +9254,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9869,7 +9269,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9884,7 +9284,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9899,7 +9299,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9914,7 +9314,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9929,7 +9329,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9944,7 +9344,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9959,7 +9359,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9974,7 +9374,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9989,7 +9389,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10004,7 +9404,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10019,7 +9419,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10034,7 +9434,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10049,7 +9449,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10064,7 +9464,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10079,7 +9479,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10094,7 +9494,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10109,7 +9509,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10124,7 +9524,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10139,7 +9539,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10154,7 +9554,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10169,7 +9569,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10184,7 +9584,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10199,7 +9599,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10214,7 +9614,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10229,7 +9629,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10244,7 +9644,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10259,7 +9659,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10274,7 +9674,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10289,7 +9689,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10304,7 +9704,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10319,7 +9719,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10334,7 +9734,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10349,7 +9749,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10364,7 +9764,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10379,7 +9779,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10394,7 +9794,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10409,7 +9809,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10424,7 +9824,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -10439,7 +9839,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -10454,7 +9854,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -10469,7 +9869,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -10484,7 +9884,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -10499,7 +9899,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -10514,7 +9914,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -10529,7 +9929,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -10544,7 +9944,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -10559,7 +9959,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -10574,7 +9974,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -10589,7 +9989,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -10604,7 +10004,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -10619,7 +10019,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -10634,7 +10034,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -10649,7 +10049,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -10664,7 +10064,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -10679,7 +10079,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -10694,7 +10094,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -10709,7 +10109,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -10724,7 +10124,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -10739,7 +10139,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -10754,7 +10154,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -10769,7 +10169,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -10784,7 +10184,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -10799,11 +10199,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10814,11 +10214,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10829,11 +10229,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10844,11 +10244,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10859,11 +10259,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10874,11 +10274,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10889,11 +10289,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10904,11 +10304,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -10919,7 +10319,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -10934,7 +10334,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -10949,7 +10349,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -10964,7 +10364,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -10979,7 +10379,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -10994,7 +10394,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -11009,7 +10409,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -11024,7 +10424,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -11039,7 +10439,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -11054,7 +10454,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -11069,7 +10469,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -11084,7 +10484,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -11099,7 +10499,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11114,7 +10514,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -11129,7 +10529,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -11144,7 +10544,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -11159,7 +10559,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -11174,7 +10574,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -11189,7 +10589,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>185</v>
+        <v>11</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -11204,7 +10604,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -11219,7 +10619,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -11234,7 +10634,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -11249,7 +10649,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -11264,7 +10664,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -11279,7 +10679,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -11294,7 +10694,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -11309,7 +10709,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>33</v>
+        <v>185</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -11324,7 +10724,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -11339,7 +10739,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -11354,7 +10754,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -11369,7 +10769,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -11384,7 +10784,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -11399,7 +10799,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -11414,7 +10814,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -12059,7 +11459,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -12074,7 +11474,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -12089,7 +11489,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -12104,7 +11504,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -12119,7 +11519,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -12134,7 +11534,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -12149,7 +11549,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -12164,7 +11564,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -12179,7 +11579,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -12194,7 +11594,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -12209,7 +11609,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -12224,7 +11624,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -12239,7 +11639,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -12254,7 +11654,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -12269,7 +11669,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>178</v>
+        <v>6</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -12284,7 +11684,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -12299,7 +11699,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -12314,7 +11714,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -12329,7 +11729,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -12344,7 +11744,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -12359,7 +11759,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -12374,7 +11774,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -12389,7 +11789,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -12404,7 +11804,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -12419,7 +11819,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -12434,7 +11834,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -12449,7 +11849,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -12464,7 +11864,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -12479,7 +11879,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -12494,7 +11894,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -12509,7 +11909,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -12524,7 +11924,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -12539,7 +11939,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -12554,7 +11954,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -12569,7 +11969,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -12584,7 +11984,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -12599,7 +11999,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -12614,7 +12014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -12629,7 +12029,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -12644,7 +12044,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -12659,7 +12059,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -12674,7 +12074,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -12689,7 +12089,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -12704,7 +12104,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -12719,7 +12119,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -12734,7 +12134,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -12749,7 +12149,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -12764,7 +12164,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -12779,7 +12179,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -12794,7 +12194,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -12809,7 +12209,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -12824,7 +12224,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -12839,7 +12239,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -12854,7 +12254,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -12869,7 +12269,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -12884,7 +12284,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -12899,7 +12299,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>177</v>
+        <v>38</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -12914,7 +12314,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -12929,7 +12329,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -12944,7 +12344,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -12959,7 +12359,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -12974,7 +12374,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -12989,7 +12389,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -13004,7 +12404,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -13019,7 +12419,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -13034,7 +12434,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -13049,7 +12449,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -13064,7 +12464,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -13079,7 +12479,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -13094,7 +12494,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -13109,7 +12509,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -13124,7 +12524,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -13139,7 +12539,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -13154,7 +12554,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -13169,7 +12569,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -13184,7 +12584,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -13199,7 +12599,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -13214,7 +12614,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -13229,7 +12629,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -13244,7 +12644,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -13259,7 +12659,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -13274,7 +12674,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -13289,7 +12689,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -13304,7 +12704,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -13319,7 +12719,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -13334,7 +12734,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -13349,7 +12749,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -13364,7 +12764,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -13379,7 +12779,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -13394,7 +12794,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -13409,7 +12809,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -13424,7 +12824,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -13439,7 +12839,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -13454,7 +12854,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -13469,7 +12869,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -13484,7 +12884,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -13499,7 +12899,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -13514,7 +12914,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -13529,7 +12929,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -13544,7 +12944,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -13559,7 +12959,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -13574,7 +12974,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -13589,7 +12989,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -13604,7 +13004,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -13619,7 +13019,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -13634,7 +13034,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -13649,7 +13049,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -13664,7 +13064,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -13679,11 +13079,11 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13694,11 +13094,11 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13709,11 +13109,11 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13724,11 +13124,11 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13739,11 +13139,11 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13754,11 +13154,11 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13769,11 +13169,11 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13184,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -13799,7 +13199,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -13814,7 +13214,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -13829,7 +13229,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -13844,7 +13244,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -13859,7 +13259,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -13874,7 +13274,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -13889,7 +13289,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -13904,7 +13304,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -13919,7 +13319,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -13934,7 +13334,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -13949,7 +13349,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -13964,7 +13364,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -13979,7 +13379,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -13994,7 +13394,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -14009,7 +13409,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -14024,7 +13424,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -14039,7 +13439,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -14054,7 +13454,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -14069,7 +13469,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -14084,7 +13484,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -14099,7 +13499,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -14114,7 +13514,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -14129,7 +13529,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -14144,7 +13544,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -14159,7 +13559,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -14174,7 +13574,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -14189,7 +13589,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -14204,7 +13604,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -14850,10 +14250,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
         <v>42</v>
@@ -14881,10 +14281,10 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I3" t="n">
         <v>36</v>
@@ -14943,7 +14343,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="4">
@@ -14953,7 +14353,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5">
@@ -15044,7 +14444,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09T10:38:54.319065+00:00</t>
+          <t>2026-10-19T13:00:59.744611+00:00</t>
         </is>
       </c>
     </row>
